--- a/tests/agent_contract/data/H4_complex_filter.xlsx
+++ b/tests/agent_contract/data/H4_complex_filter.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户订单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,4331 +413,4178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>客户类型</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>订单金额</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>支付状态</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>订单状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>订单号</t>
+          <t>O40001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>客户等级</t>
+          <t>企业</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>订单金额</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>支付方式</t>
-        </is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6489</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>是否开票</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>区域</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O40001</t>
+          <t>O40002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>6873</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7774</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O40002</t>
+          <t>O40003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>5516</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5992</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O40003</t>
+          <t>O40004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>6161</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7050</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O40004</t>
+          <t>O40005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>5232</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5750</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O40005</t>
+          <t>O40006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>7328</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5808</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O40006</t>
+          <t>O40007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>6464</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7282</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O40007</t>
+          <t>O40008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>6962</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7182</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O40008</t>
+          <t>O40009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>7686</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6215</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O40009</t>
+          <t>O40010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>6442</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6643</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O40010</t>
+          <t>O40011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>7497</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6578</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O40011</t>
+          <t>O40012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>7643</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6271</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O40012</t>
+          <t>O40013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>7118</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5770</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O40013</t>
+          <t>O40014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>6052</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>8000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O40014</t>
+          <t>O40015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>5453</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5565</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O40015</t>
+          <t>O40016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>5369</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7713</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O40016</t>
+          <t>O40017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>5056</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5469</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O40017</t>
+          <t>O40018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>5604</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13449</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O40018</t>
+          <t>O40019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>5202</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>8349</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O40019</t>
+          <t>O40020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>6227</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3204</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O40020</t>
+          <t>O40021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>5115</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>7593</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O40021</t>
+          <t>O40022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>2188</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5096</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>O40022</t>
+          <t>O40023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>4404</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>8481</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>O40023</t>
+          <t>O40024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>3383</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>9852</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>O40024</t>
+          <t>O40025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1412</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>9759</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>O40025</t>
+          <t>O40026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>2166</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4507</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>O40026</t>
+          <t>O40027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>4741</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>4723</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>O40027</t>
+          <t>O40028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1331</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1876</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>O40028</t>
+          <t>O40029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>3977</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>6050</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>O40029</t>
+          <t>O40030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>2928</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>4274</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>O40030</t>
+          <t>O40031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>9205</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>7227</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>O40031</t>
+          <t>O40032</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>3989</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>8665</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>O40032</t>
+          <t>O40033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>8291</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>7304</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>O40033</t>
+          <t>O40034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>8961</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>8668</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>O40034</t>
+          <t>O40035</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>1140</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>9248</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>O40035</t>
+          <t>O40036</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>9269</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3885</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>O40036</t>
+          <t>O40037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>4802</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>8086</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>O40037</t>
+          <t>O40038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>9240</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>6805</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>O40038</t>
+          <t>O40039</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>9653</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1835</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>O40039</t>
+          <t>O40040</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>2380</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3119</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>O40040</t>
+          <t>O40041</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>9798</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>9900</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>O40041</t>
+          <t>O40042</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>8717</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>4420</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>O40042</t>
+          <t>O40043</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>3816</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3314</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>O40043</t>
+          <t>O40044</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>5061</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>6598</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>O40044</t>
+          <t>O40045</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>9844</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3482</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>O40045</t>
+          <t>O40046</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
         <v>5001</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>O40046</t>
+          <t>O40047</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
         <v>5001</v>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>O40047</t>
+          <t>O40048</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>5001</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>O40048</t>
+          <t>O40049</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
         <v>5001</v>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>O40049</t>
+          <t>O40050</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
         <v>5001</v>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>O40050</t>
+          <t>O40051</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
         <v>5001</v>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>O40051</t>
+          <t>O40052</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
         <v>5001</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>O40052</t>
+          <t>O40053</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>5001</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>O40053</t>
+          <t>O40054</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
         <v>5001</v>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>O40054</t>
+          <t>O40055</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
         <v>5001</v>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>O40055</t>
+          <t>O40056</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
         <v>5001</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>O40056</t>
+          <t>O40057</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
         <v>5001</v>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>O40057</t>
+          <t>O40058</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
         <v>5001</v>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>O40058</t>
+          <t>O40059</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
         <v>5001</v>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>O40059</t>
+          <t>O40060</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
         <v>5001</v>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>O40060</t>
+          <t>O40061</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
         <v>5001</v>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>O40061</t>
+          <t>O40062</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
         <v>5001</v>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>O40062</t>
+          <t>O40063</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
         <v>5001</v>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>O40063</t>
+          <t>O40064</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
         <v>5001</v>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>O40064</t>
+          <t>O40065</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
         <v>5001</v>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>O40065</t>
+          <t>O40066</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>-2020</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>5001</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>O40066</t>
+          <t>O40067</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>2410</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>5001</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>O40067</t>
+          <t>O40068</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>7406</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>5001</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>O40068</t>
+          <t>O40069</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>1287</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>5001</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>O40069</t>
+          <t>O40070</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>2489</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>-22024</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>O40070</t>
+          <t>O40071</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>1684</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1299</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>O40071</t>
+          <t>O40072</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>9730</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2773</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>O40072</t>
+          <t>O40073</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>8222</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2192</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>O40073</t>
+          <t>O40074</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>7199</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>9037</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>O40074</t>
+          <t>O40075</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>4476</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>5447</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>O40075</t>
+          <t>O40076</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>7289</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>4053</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>O40076</t>
+          <t>O40077</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>5742</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>8631</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>O40077</t>
+          <t>O40078</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>8830</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>9965</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>O40078</t>
+          <t>O40079</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>1787</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>5745</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>O40079</t>
+          <t>O40080</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>9847</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>4806</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>O40080</t>
+          <t>O40081</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>7022</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>4849</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>O40081</t>
+          <t>O40082</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>9584</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>4718</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>O40082</t>
+          <t>O40083</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>2008</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>9640</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>O40083</t>
+          <t>O40084</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>8188</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>8092</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>O40084</t>
+          <t>O40085</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>9646</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>2937</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>O40085</t>
+          <t>O40086</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>7774</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>6580</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>O40086</t>
+          <t>O40087</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>4506</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1292</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>O40087</t>
+          <t>O40088</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>6174</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>8463</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>O40088</t>
+          <t>O40089</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>7603</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>3035</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>O40089</t>
+          <t>O40090</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>3093</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1137</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>O40090</t>
+          <t>O40091</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>2587</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>6218</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>O40091</t>
+          <t>O40092</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>2359</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>3705</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>O40092</t>
+          <t>O40093</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>4202</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>6624</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>O40093</t>
+          <t>O40094</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>9993</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>5200</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>O40094</t>
+          <t>O40095</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>5104</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>5080</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>O40095</t>
+          <t>O40096</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>7731</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>5037</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>O40096</t>
+          <t>O40097</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>7223</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>5048</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>O40097</t>
+          <t>O40098</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>6964</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>5001</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>O40098</t>
+          <t>O40099</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>5060</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>5001</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>O40099</t>
+          <t>O40100</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
         <v>5001</v>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>O40100</t>
+          <t>O40101</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>5005</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>5001</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>O40101</t>
+          <t>O40102</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
         <v>5001</v>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>O40102</t>
+          <t>O40103</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>5004</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>5001</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>O40103</t>
+          <t>O40104</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>5004</v>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>5001</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>O40104</t>
+          <t>O40105</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
         <v>5001</v>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>O40105</t>
+          <t>O40106</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>5002</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>5001</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>O40106</t>
+          <t>O40107</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
         <v>5001</v>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>O40107</t>
+          <t>O40108</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
         <v>5001</v>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>O40108</t>
+          <t>O40109</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>5001</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>2632</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>O40109</t>
+          <t>O40110</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>5001</v>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1466</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>O40110</t>
+          <t>O40111</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>1644</v>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>3063</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>O40111</t>
+          <t>O40112</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>8016</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>8367</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>O40112</t>
+          <t>O40113</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>1631</v>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>8528</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>O40113</t>
+          <t>O40114</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>9433</v>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>7977</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>O40114</t>
+          <t>O40115</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>3133</v>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1024</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>O40115</t>
+          <t>O40116</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>5896</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>8446</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>O40116</t>
+          <t>O40117</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>7819</v>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>6879</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>O40117</t>
+          <t>O40118</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>9034</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>2823</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>O40118</t>
+          <t>O40119</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>6534</v>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>5412</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>O40119</t>
+          <t>O40120</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>5051</v>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>3186</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>O40120</t>
+          <t>O40121</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>6631</v>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>5196</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>O40121</t>
+          <t>O40122</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>2646</v>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>9789</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>O40122</t>
+          <t>O40123</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>5634</v>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>9850</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>O40123</t>
+          <t>O40124</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>5764</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>4754</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>O40124</t>
+          <t>O40125</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>6224</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>货到付款</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>9670</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>O40125</t>
+          <t>O40126</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>4952</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>2756</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>O40126</t>
+          <t>O40127</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>8427</v>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>6895</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>O40127</t>
+          <t>O40128</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>2473</v>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>2439</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>O40128</t>
+          <t>O40129</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>1623</v>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>7978</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>O40129</t>
+          <t>O40130</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>9377</v>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>5824</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>O40130</t>
+          <t>O40131</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>7102</v>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>2667</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>O40131</t>
+          <t>O40132</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>6075</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1844</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>O40132</t>
+          <t>O40133</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>3079</v>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>5235</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>进行中</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>O40133</t>
+          <t>O40134</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>3635</v>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>8501</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>已退款</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>O40134</t>
+          <t>O40135</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>7680</v>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>4807</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>O40135</t>
+          <t>O40136</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>5691</v>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>8239</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>O40136</t>
+          <t>O40137</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>8291</v>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>9156</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>O40137</t>
+          <t>O40138</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>6295</v>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>5275</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>未支付</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>华北</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>O40138</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>6875</v>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>O40139</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>7379</v>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>O40140</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>钻石</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>9868</v>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>O40141</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>4692</v>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>O40142</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>5300</v>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>对公转账</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>O40143</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>3835</v>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>在线支付</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>华北</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
